--- a/DataTables/Usuarios.xlsx
+++ b/DataTables/Usuarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AlborAutomation\albor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C54D6F7-1D0F-4341-9960-810B69DEA2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E45A88-1264-4E3B-94D1-C40864DEECC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>url</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>P@ro040724</t>
+  </si>
+  <si>
+    <t>P@ro040727</t>
   </si>
 </sst>
 </file>
@@ -398,7 +401,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/DataTables/Usuarios.xlsx
+++ b/DataTables/Usuarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AlborAutomation\albor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E45A88-1264-4E3B-94D1-C40864DEECC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FE6C24-8B52-4BB5-839C-7A6EF6B02691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <t>P@ro040724</t>
   </si>
   <si>
-    <t>P@ro040727</t>
+    <t>P@ro040729</t>
   </si>
 </sst>
 </file>
